--- a/tame_output/ON/bt/strategyON_20240225.xlsx
+++ b/tame_output/ON/bt/strategyON_20240225.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>1.416703567712729</v>
+        <v>1.416751948246173</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.725385449593377</v>
+        <v>3.725404801806755</v>
       </c>
       <c r="F1884" t="n">
-        <v>2.455213385121427</v>
+        <v>2.455142101625289</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.632188477894889</v>
+        <v>4.632145707797206</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240225.xlsx
+++ b/tame_output/ON/bt/strategyON_20240225.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.7%</t>
+          <t>447.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>1.416751948246173</v>
+        <v>1.41588777608682</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.725404801806755</v>
+        <v>3.725059132943014</v>
       </c>
       <c r="F1884" t="n">
-        <v>2.455142101625289</v>
+        <v>2.454108384732936</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.632145707797206</v>
+        <v>4.631525477661794</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240225.xlsx
+++ b/tame_output/ON/bt/strategyON_20240225.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.8%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-25.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>130.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>1.41588777608682</v>
+        <v>1.360160968898378</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.725059132943014</v>
+        <v>3.702768410067637</v>
       </c>
       <c r="F1884" t="n">
-        <v>2.454108384732936</v>
+        <v>2.370493574077075</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.631525477661794</v>
+        <v>4.581356591268278</v>
       </c>
     </row>
   </sheetData>
